--- a/03_BOM/BE-PC_EXP_V100_6JAN.xlsx
+++ b/03_BOM/BE-PC_EXP_V100_6JAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_AltiumProject\17_BEE_PC_EXP_V100\baobuibk-NANORACK_4U_EXP_HW_1.0.0\03_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD8B585-3246-4361-904D-D2D4552908BE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102BAF71-334E-4458-AF62-C78DC11E1B4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="11544" xr2:uid="{3AAC5DB9-5F77-4C7D-A8C8-27E247D767E8}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="411">
   <si>
     <t>Line #</t>
   </si>
@@ -1243,6 +1243,24 @@
   </si>
   <si>
     <t>Cùng part line 8</t>
+  </si>
+  <si>
+    <t>Option 2 10R</t>
+  </si>
+  <si>
+    <t>Option 1 20R</t>
+  </si>
+  <si>
+    <t>RES 10 OHM 5% 1.5W 2512</t>
+  </si>
+  <si>
+    <t>RPC2512JT10R0</t>
+  </si>
+  <si>
+    <t>CRM2512-FX-20R0ELF</t>
+  </si>
+  <si>
+    <t>RES SMD 20 OHM 1% 2W 2512</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -1328,6 +1346,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1642,7 +1661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EE5494A-6E0C-43FD-B1AE-FFC802290BE4}">
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1652,6 +1671,7 @@
     <col min="6" max="6" width="27.69921875" customWidth="1"/>
     <col min="7" max="7" width="36.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3310,7 +3330,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>67</v>
       </c>
@@ -3339,7 +3359,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>68</v>
       </c>
@@ -3368,7 +3388,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>70</v>
       </c>
@@ -3397,7 +3417,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>71</v>
       </c>
@@ -3422,575 +3442,591 @@
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="10">
         <v>72</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="10">
         <v>15</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E69" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
+      <c r="F69" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>410</v>
+      </c>
       <c r="I69" s="9" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
+      <c r="J69" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="10">
+        <v>72</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C70" s="10">
+        <v>15</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="J70" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
         <v>73</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B71" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C71" s="6">
         <v>1</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D71" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="E71" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F71" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="G70" s="7" t="s">
+      <c r="G71" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="H70" s="7" t="s">
+      <c r="H71" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="I70" s="7" t="s">
+      <c r="I71" s="7" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
         <v>74</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B72" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C72" s="2">
         <v>2</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="I71" s="9" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>75</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C72" s="2">
-        <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>381</v>
+        <v>340</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="I72" s="9" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C73" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>381</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I73" s="9" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C74" s="2">
         <v>2</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>323</v>
+        <v>381</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>129</v>
       </c>
       <c r="E75" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>78</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C76" s="2">
+        <v>1</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F76" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="G76" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="I75" s="9" t="s">
+      <c r="I76" s="9" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
         <v>79</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B77" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C77" s="2">
         <v>8</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
         <v>80</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="C77" s="2">
-        <v>1</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="H77" s="1"/>
-      <c r="I77" s="9" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>81</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>345</v>
+        <v>231</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>200</v>
+        <v>344</v>
       </c>
       <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I78" s="9" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>268</v>
+        <v>345</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>346</v>
+        <v>200</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C80" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>347</v>
+        <v>268</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>206</v>
+        <v>346</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C81" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C82" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>252</v>
+        <v>348</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C83" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+      <c r="A84" s="2">
+        <v>86</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C84" s="2">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
         <v>87</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B85" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C85" s="6">
         <v>1</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D85" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="E84" s="6" t="s">
+      <c r="E85" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="F84" s="7">
+      <c r="F85" s="7">
         <v>0</v>
       </c>
-      <c r="G84" s="7">
+      <c r="G85" s="7">
         <v>0</v>
       </c>
-      <c r="H84" s="7"/>
-      <c r="I84" s="7" t="s">
+      <c r="H85" s="7"/>
+      <c r="I85" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="J84" s="8"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
-        <v>88</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C85" s="2">
-        <v>8</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
+      <c r="J85" s="8"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C86" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>351</v>
+        <v>219</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C87" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>225</v>
+        <v>53</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>224</v>
+        <v>351</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C88" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C89" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="H89" s="1"/>
-      <c r="I89" s="9" t="s">
-        <v>363</v>
-      </c>
+      <c r="I89" s="1"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C90" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>230</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="9" t="s">
@@ -3999,252 +4035,250 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C91" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>354</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="F91" s="1"/>
       <c r="G91" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
+      <c r="I91" s="9" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>252</v>
+        <v>354</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>355</v>
+        <v>252</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>53</v>
+        <v>244</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>252</v>
+        <v>355</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>249</v>
+        <v>53</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>252</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C96" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F96" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="G96" s="2" t="s">
-        <v>251</v>
+      <c r="G96" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C97" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>252</v>
+        <v>325</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>356</v>
+        <v>252</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H99" s="1"/>
-      <c r="I99" s="9" t="s">
-        <v>363</v>
-      </c>
+      <c r="I99" s="1"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>52</v>
+        <v>356</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="9" t="s">
@@ -4253,129 +4287,129 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
+      <c r="I101" s="9" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>268</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H102" s="1"/>
-      <c r="I102" s="9" t="s">
-        <v>363</v>
-      </c>
+      <c r="I102" s="1"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C103" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>252</v>
+        <v>272</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>268</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
+      <c r="I103" s="9" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>279</v>
+        <v>204</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F104" s="1">
-        <v>0</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="H104" s="1"/>
-      <c r="I104" s="9" t="s">
-        <v>363</v>
-      </c>
+      <c r="I104" s="1"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>252</v>
+        <v>278</v>
+      </c>
+      <c r="F105" s="1">
+        <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>403</v>
+        <v>278</v>
       </c>
       <c r="H105" s="1"/>
       <c r="I105" s="9" t="s">
@@ -4384,102 +4418,102 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C106" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>252</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>284</v>
+        <v>403</v>
       </c>
       <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
+      <c r="I106" s="9" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C107" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>6</v>
+        <v>284</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>357</v>
+        <v>252</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C108" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>291</v>
+        <v>6</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="H108" s="1"/>
-      <c r="I108" s="9" t="s">
-        <v>363</v>
-      </c>
+      <c r="I108" s="1"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C109" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>231</v>
+        <v>290</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H109" s="1"/>
       <c r="I109" s="9" t="s">
@@ -4488,25 +4522,25 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>299</v>
+        <v>231</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="9" t="s">
@@ -4515,28 +4549,55 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="H111" s="1"/>
       <c r="I111" s="9" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>114</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C112" s="2">
+        <v>1</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H112" s="1"/>
+      <c r="I112" s="9" t="s">
         <v>363</v>
       </c>
     </row>

--- a/03_BOM/BE-PC_EXP_V100_6JAN.xlsx
+++ b/03_BOM/BE-PC_EXP_V100_6JAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_AltiumProject\17_BEE_PC_EXP_V100\baobuibk-NANORACK_4U_EXP_HW_1.0.0\03_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102BAF71-334E-4458-AF62-C78DC11E1B4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6E5354-7547-438F-AF37-186889E2B6D5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="11544" xr2:uid="{3AAC5DB9-5F77-4C7D-A8C8-27E247D767E8}"/>
   </bookViews>
@@ -573,9 +573,6 @@
     <t>16.5k/1%</t>
   </si>
   <si>
-    <t>R546, R597, R598, R599, R600, R601, R602, R603, R604, R605, R606, R607, R608, R609, R610</t>
-  </si>
-  <si>
     <t>20R/2W/5V 10R/1W/3V</t>
   </si>
   <si>
@@ -1261,6 +1258,9 @@
   </si>
   <si>
     <t>RES SMD 20 OHM 1% 2W 2512</t>
+  </si>
+  <si>
+    <t>R546, R597, R598, R599, R600, R601, R602, R603, R604, R605, R606, R607, R608, R609, R610, R611</t>
   </si>
 </sst>
 </file>
@@ -1682,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>5</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1724,7 +1724,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1745,13 +1745,13 @@
         <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1778,7 +1778,7 @@
         <v>18</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1805,7 +1805,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1832,7 +1832,7 @@
         <v>25</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1841,7 +1841,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C7" s="2">
         <v>6</v>
@@ -1853,13 +1853,13 @@
         <v>26</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -1880,13 +1880,13 @@
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1910,13 +1910,13 @@
         <v>14</v>
       </c>
       <c r="G9" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>362</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1942,7 +1942,7 @@
         <v>33</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -1963,13 +1963,13 @@
         <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="I11" s="1"/>
     </row>
@@ -1993,13 +1993,13 @@
         <v>14</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2022,10 +2022,10 @@
         <v>113</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I13" s="1"/>
     </row>
@@ -2049,10 +2049,10 @@
         <v>14</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -2073,16 +2073,16 @@
         <v>24</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2090,7 +2090,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
@@ -2102,16 +2102,16 @@
         <v>45</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="I16" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -2137,7 +2137,7 @@
         <v>47</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I17" s="1"/>
     </row>
@@ -2183,7 +2183,7 @@
         <v>55</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>55</v>
@@ -2208,10 +2208,10 @@
         <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -2233,7 +2233,7 @@
         <v>61</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>61</v>
@@ -2261,7 +2261,7 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -2284,7 +2284,7 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -2332,7 +2332,7 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -2577,10 +2577,10 @@
         <v>102</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2602,10 +2602,10 @@
         <v>6</v>
       </c>
       <c r="F36" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2677,7 +2677,7 @@
         <v>117</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>117</v>
@@ -2752,10 +2752,10 @@
         <v>128</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -2777,10 +2777,10 @@
         <v>131</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -2790,7 +2790,7 @@
         <v>45</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2">
         <v>193</v>
@@ -2802,10 +2802,10 @@
         <v>132</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -2827,14 +2827,14 @@
         <v>134</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2854,10 +2854,10 @@
         <v>136</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -2879,10 +2879,10 @@
         <v>138</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -2904,10 +2904,10 @@
         <v>140</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -2929,10 +2929,10 @@
         <v>142</v>
       </c>
       <c r="F49" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -2954,14 +2954,14 @@
         <v>144</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2981,10 +2981,10 @@
         <v>146</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -3006,10 +3006,10 @@
         <v>148</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -3031,10 +3031,10 @@
         <v>150</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -3056,14 +3056,14 @@
         <v>102</v>
       </c>
       <c r="F54" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="G54" s="7" t="s">
         <v>323</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>324</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -3083,10 +3083,10 @@
         <v>153</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -3108,10 +3108,10 @@
         <v>155</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -3133,14 +3133,14 @@
         <v>157</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H57" s="7"/>
       <c r="I57" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -3160,10 +3160,10 @@
         <v>159</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -3185,10 +3185,10 @@
         <v>142</v>
       </c>
       <c r="F59" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -3210,10 +3210,10 @@
         <v>162</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -3248,7 +3248,7 @@
         <v>64</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C62" s="2">
         <v>72</v>
@@ -3260,16 +3260,16 @@
         <v>132</v>
       </c>
       <c r="F62" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="I62" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -3289,16 +3289,16 @@
         <v>170</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -3318,16 +3318,16 @@
         <v>172</v>
       </c>
       <c r="F64" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="I64" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -3347,16 +3347,16 @@
         <v>174</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G65" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="I65" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -3376,16 +3376,16 @@
         <v>176</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -3405,16 +3405,16 @@
         <v>178</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -3434,10 +3434,10 @@
         <v>180</v>
       </c>
       <c r="F68" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>341</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -3447,31 +3447,31 @@
         <v>72</v>
       </c>
       <c r="B69" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="C69" s="10">
+        <v>16</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E69" s="10" t="s">
         <v>181</v>
-      </c>
-      <c r="C69" s="10">
-        <v>15</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>182</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>108</v>
       </c>
       <c r="G69" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="H69" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="H69" s="5" t="s">
-        <v>410</v>
-      </c>
       <c r="I69" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J69" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -3479,31 +3479,31 @@
         <v>72</v>
       </c>
       <c r="B70" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="C70" s="10">
+        <v>16</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E70" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C70" s="10">
-        <v>15</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>182</v>
-      </c>
       <c r="F70" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J70" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -3511,7 +3511,7 @@
         <v>73</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C71" s="6">
         <v>1</v>
@@ -3520,19 +3520,19 @@
         <v>129</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H71" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="I71" s="7" t="s">
         <v>392</v>
-      </c>
-      <c r="I71" s="7" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -3540,7 +3540,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C72" s="2">
         <v>2</v>
@@ -3549,19 +3549,19 @@
         <v>168</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -3569,7 +3569,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -3581,16 +3581,16 @@
         <v>162</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G73" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="H73" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="H73" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="I73" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -3598,7 +3598,7 @@
         <v>76</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C74" s="2">
         <v>2</v>
@@ -3610,16 +3610,16 @@
         <v>159</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -3627,7 +3627,7 @@
         <v>77</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C75" s="2">
         <v>2</v>
@@ -3636,13 +3636,13 @@
         <v>129</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -3652,7 +3652,7 @@
         <v>78</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -3661,19 +3661,19 @@
         <v>129</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G76" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="H76" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="H76" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="I76" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -3681,22 +3681,22 @@
         <v>79</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C77" s="2">
         <v>8</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -3706,26 +3706,26 @@
         <v>80</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -3733,22 +3733,22 @@
         <v>81</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -3758,22 +3758,22 @@
         <v>82</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -3783,22 +3783,22 @@
         <v>83</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C81" s="2">
         <v>4</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -3808,22 +3808,22 @@
         <v>84</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -3833,22 +3833,22 @@
         <v>85</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C83" s="2">
         <v>4</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -3858,7 +3858,7 @@
         <v>86</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -3867,13 +3867,13 @@
         <v>118</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -3883,16 +3883,16 @@
         <v>87</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C85" s="6">
         <v>1</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F85" s="7">
         <v>0</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="H85" s="7"/>
       <c r="I85" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J85" s="8"/>
     </row>
@@ -3911,22 +3911,22 @@
         <v>88</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C86" s="2">
         <v>8</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -3936,7 +3936,7 @@
         <v>89</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C87" s="2">
         <v>2</v>
@@ -3945,13 +3945,13 @@
         <v>53</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F87" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G87" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -3961,22 +3961,22 @@
         <v>90</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -3986,22 +3986,22 @@
         <v>91</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C89" s="2">
         <v>4</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -4011,26 +4011,26 @@
         <v>92</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E90" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F90" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="G90" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -4038,24 +4038,24 @@
         <v>93</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C91" s="2">
         <v>2</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -4063,22 +4063,22 @@
         <v>94</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -4088,22 +4088,22 @@
         <v>95</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -4113,22 +4113,22 @@
         <v>96</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -4138,7 +4138,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -4147,13 +4147,13 @@
         <v>53</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
@@ -4163,22 +4163,22 @@
         <v>98</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
@@ -4188,22 +4188,22 @@
         <v>99</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C97" s="2">
         <v>3</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E97" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F97" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="G97" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
@@ -4213,22 +4213,22 @@
         <v>100</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
@@ -4238,22 +4238,22 @@
         <v>101</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
@@ -4263,26 +4263,26 @@
         <v>102</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -4290,26 +4290,26 @@
         <v>103</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>52</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H101" s="1"/>
       <c r="I101" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -4317,22 +4317,22 @@
         <v>104</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E102" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="G102" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
@@ -4342,26 +4342,26 @@
         <v>105</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E103" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -4369,22 +4369,22 @@
         <v>106</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C104" s="2">
         <v>2</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
@@ -4394,26 +4394,26 @@
         <v>107</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H105" s="1"/>
       <c r="I105" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -4421,26 +4421,26 @@
         <v>108</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H106" s="1"/>
       <c r="I106" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -4448,22 +4448,22 @@
         <v>109</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C107" s="2">
         <v>3</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
@@ -4473,22 +4473,22 @@
         <v>110</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F108" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G108" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
@@ -4498,26 +4498,26 @@
         <v>111</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C109" s="2">
         <v>2</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E109" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F109" s="2" t="s">
+      <c r="G109" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="H109" s="1"/>
       <c r="I109" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -4525,26 +4525,26 @@
         <v>112</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E110" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>295</v>
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -4552,26 +4552,26 @@
         <v>113</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E111" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F111" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="F111" s="2" t="s">
+      <c r="G111" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="H111" s="1"/>
       <c r="I111" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -4579,26 +4579,26 @@
         <v>114</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E112" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G112" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
